--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -499,7 +499,7 @@
     <t>Code de l'entrée en LOINC</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260916095454</t>
   </si>
   <si>
     <t>Organizer.sdtcText</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="238">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -604,73 +604,33 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>Organizer.component:frResultat</t>
-  </si>
-  <si>
-    <t>frResultat</t>
-  </si>
-  <si>
-    <t>Organizer.component:frResultat.nullFlavor</t>
-  </si>
-  <si>
     <t>Organizer.component.nullFlavor</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.realmCode</t>
-  </si>
-  <si>
     <t>Organizer.component.realmCode</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.typeId</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.typeId.nullFlavor</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.nullFlavor</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.assigningAuthorityName</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.typeId.displayable</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.displayable</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.typeId.root</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.root</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.typeId.extension</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.extension</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.templateId</t>
-  </si>
-  <si>
     <t>Organizer.component.templateId</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.typeCode</t>
-  </si>
-  <si>
     <t>Organizer.component.typeCode</t>
   </si>
   <si>
@@ -683,9 +643,6 @@
     <t>OrganizerComponent.typeCode</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.contextConductionInd</t>
-  </si>
-  <si>
     <t>Organizer.component.contextConductionInd</t>
   </si>
   <si>
@@ -693,9 +650,6 @@
   </si>
   <si>
     <t>OrganizerComponent.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Organizer.component:frResultat.sequenceNumber</t>
   </si>
   <si>
     <t>Organizer.component.sequenceNumber</t>
@@ -708,16 +662,10 @@
     <t>OrganizerComponent.sequenceNumber</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.sdtcPriorityNumber</t>
-  </si>
-  <si>
     <t>Organizer.component.sdtcPriorityNumber</t>
   </si>
   <si>
     <t>OrganizerComponent.sdtcPriorityNumber</t>
-  </si>
-  <si>
-    <t>Organizer.component:frResultat.seperatableInd</t>
   </si>
   <si>
     <t>Organizer.component.seperatableInd</t>
@@ -730,9 +678,6 @@
     <t>OrganizerComponent.seperatableInd</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.act</t>
-  </si>
-  <si>
     <t>Organizer.component.act</t>
   </si>
   <si>
@@ -743,9 +688,6 @@
     <t>OrganizerComponent.act</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.encounter</t>
-  </si>
-  <si>
     <t>Organizer.component.encounter</t>
   </si>
   <si>
@@ -756,9 +698,6 @@
     <t>OrganizerComponent.encounter</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.observation</t>
-  </si>
-  <si>
     <t>Organizer.component.observation</t>
   </si>
   <si>
@@ -772,9 +711,6 @@
     <t>OrganizerComponent.observation</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.observationMedia</t>
-  </si>
-  <si>
     <t>Organizer.component.observationMedia</t>
   </si>
   <si>
@@ -785,9 +721,6 @@
     <t>OrganizerComponent.observationMedia</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.organizer</t>
-  </si>
-  <si>
     <t>Organizer.component.organizer</t>
   </si>
   <si>
@@ -798,9 +731,6 @@
     <t>OrganizerComponent.organizer</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.procedure</t>
-  </si>
-  <si>
     <t>Organizer.component.procedure</t>
   </si>
   <si>
@@ -811,9 +741,6 @@
     <t>OrganizerComponent.procedure</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.regionOfInterest</t>
-  </si>
-  <si>
     <t>Organizer.component.regionOfInterest</t>
   </si>
   <si>
@@ -824,9 +751,6 @@
     <t>OrganizerComponent.regionOfInterest</t>
   </si>
   <si>
-    <t>Organizer.component:frResultat.substanceAdministration</t>
-  </si>
-  <si>
     <t>Organizer.component.substanceAdministration</t>
   </si>
   <si>
@@ -835,9 +759,6 @@
   </si>
   <si>
     <t>OrganizerComponent.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Organizer.component:frResultat.supply</t>
   </si>
   <si>
     <t>Organizer.component.supply</t>
@@ -1164,10 +1085,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK59"/>
+  <dimension ref="A1:AK58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.58203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.59375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.34765625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
@@ -4653,7 +4574,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>184</v>
       </c>
@@ -4669,7 +4590,7 @@
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>142</v>
@@ -4722,14 +4643,16 @@
         <v>75</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AC35" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>184</v>
@@ -4752,20 +4675,20 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>76</v>
@@ -4780,10 +4703,12 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
+      <c r="M36" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -4809,13 +4734,11 @@
         <v>75</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -4833,13 +4756,13 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>75</v>
@@ -4853,23 +4776,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E37" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -4881,11 +4802,11 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4912,11 +4833,13 @@
         <v>75</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>75</v>
@@ -4934,13 +4857,13 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>75</v>
@@ -4954,10 +4877,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4968,7 +4891,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -4980,11 +4903,11 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5035,19 +4958,19 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -5055,16 +4978,18 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F39" t="s" s="2">
         <v>81</v>
       </c>
@@ -5081,11 +5006,11 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5112,13 +5037,11 @@
         <v>75</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>75</v>
@@ -5136,7 +5059,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5148,7 +5071,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5156,17 +5079,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>81</v>
@@ -5184,11 +5107,11 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5215,11 +5138,13 @@
         <v>75</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>75</v>
@@ -5237,7 +5162,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5257,17 +5182,17 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>81</v>
@@ -5285,11 +5210,11 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5340,7 +5265,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -5360,20 +5285,20 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>76</v>
@@ -5388,11 +5313,11 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5401,7 +5326,7 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>75</v>
@@ -5443,7 +5368,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -5463,17 +5388,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>76</v>
@@ -5491,11 +5416,11 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5504,7 +5429,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>75</v>
@@ -5546,7 +5471,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -5566,23 +5491,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E44" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>75</v>
@@ -5594,11 +5517,11 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5649,13 +5572,13 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>75</v>
@@ -5669,10 +5592,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5683,7 +5606,7 @@
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -5695,16 +5618,14 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L45" s="2"/>
-      <c r="M45" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>75</v>
+        <v>196</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
@@ -5726,13 +5647,11 @@
         <v>75</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>75</v>
@@ -5750,13 +5669,13 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>125</v>
+        <v>198</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
@@ -5770,10 +5689,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5796,18 +5715,18 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>75</v>
@@ -5825,11 +5744,13 @@
         <v>75</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>75</v>
@@ -5847,7 +5768,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -5867,10 +5788,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5893,7 +5814,7 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -5904,7 +5825,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>214</v>
+        <v>75</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>75</v>
@@ -5946,7 +5867,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -5966,10 +5887,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5992,7 +5913,7 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6045,7 +5966,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6065,10 +5986,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6091,7 +6012,7 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6144,7 +6065,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -6164,10 +6085,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6190,7 +6111,7 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6243,7 +6164,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -6263,10 +6184,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6289,7 +6210,7 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6342,7 +6263,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -6362,10 +6283,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6373,7 +6294,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>76</v>
@@ -6388,10 +6309,14 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6441,7 +6366,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -6461,10 +6386,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6487,14 +6412,10 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6544,7 +6465,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -6564,10 +6485,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6590,7 +6511,7 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6643,7 +6564,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -6663,10 +6584,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6689,7 +6610,7 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6742,7 +6663,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -6762,10 +6683,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6788,7 +6709,7 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6841,7 +6762,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -6861,10 +6782,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6887,7 +6808,7 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -6940,7 +6861,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -6960,10 +6881,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6986,7 +6907,7 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7039,7 +6960,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -7057,107 +6978,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK59">
+  <autoFilter ref="A1:AK58">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7167,7 +6989,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI58">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
